--- a/results/Int All Data 0.4/Rando_9_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_9_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.817226403225126</v>
+        <v>0.8269261381725566</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8154355722795672</v>
+        <v>0.8283588029290034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8161988929931762</v>
+        <v>0.8283588029290034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.817038449883584</v>
+        <v>0.8161049163224052</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.827530753386037</v>
+        <v>0.8161049163224052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.827530753386037</v>
+        <v>0.8139266713463214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8248533772146849</v>
+        <v>0.8145960153891594</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8271903276908974</v>
+        <v>0.8153123477673828</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8255874500868805</v>
+        <v>0.8161988929931762</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8245129515195453</v>
+        <v>0.8165100708469024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.824871117708657</v>
+        <v>0.8246069281903161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8250413305562269</v>
+        <v>0.8246069281903161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8250413305562269</v>
+        <v>0.8265387241420313</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8332853860523277</v>
+        <v>0.8315353102956238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8288819077647744</v>
+        <v>0.8315353102956238</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8285237415756628</v>
+        <v>0.8327800217105288</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8331799020341155</v>
+        <v>0.8166980241884443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8296274879844114</v>
+        <v>0.8226281439032155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8310069312589421</v>
+        <v>0.8229863100923274</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8292161003133833</v>
+        <v>0.8140029075231201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8305547883990594</v>
+        <v>0.8092465372473658</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8298854443562214</v>
+        <v>0.8092465372473658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8306017767344449</v>
+        <v>0.8112536104302597</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8293570653195399</v>
+        <v>0.8005910940802369</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8293570653195399</v>
+        <v>0.7983481202747955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8001816243004491</v>
+        <v>0.8013189338059017</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8046205835759466</v>
+        <v>0.7995281028603429</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7935591458479572</v>
+        <v>0.8011017326229464</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7854507811571021</v>
+        <v>0.7971973855306613</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7924553994392086</v>
+        <v>0.8004208812326671</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7962072741778959</v>
+        <v>0.7915722105230857</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8045568136922092</v>
+        <v>0.7879435602965827</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8131350617369191</v>
+        <v>0.7879435602965827</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8298864033018416</v>
+        <v>0.786968312600929</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.827925359508713</v>
+        <v>0.7938789542122645</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8465845233848479</v>
+        <v>0.8043127620318906</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8505713398004626</v>
+        <v>0.8071603510508125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8440063980851773</v>
+        <v>0.7999970272685777</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8429318995178421</v>
+        <v>0.8025041905923599</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8425737333287304</v>
+        <v>0.8151694648699861</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8425737333287304</v>
+        <v>0.815527631059098</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8425737333287304</v>
+        <v>0.8162439634373214</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8254872402695788</v>
+        <v>0.8222565524754222</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8010796768736839</v>
+        <v>0.8193442346271428</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8040859713927342</v>
+        <v>0.8266955117509196</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8018899859226782</v>
+        <v>0.8097677241918966</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8034166273498963</v>
+        <v>0.8115585551374553</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8001638838064771</v>
+        <v>0.8117465084789972</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8018429975872928</v>
+        <v>0.805928105928969</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8018429975872928</v>
+        <v>0.7815028020391019</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8091880415645389</v>
+        <v>0.7777979156358001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8091880415645389</v>
+        <v>0.7774397494466884</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8022419189652593</v>
+        <v>0.7717853265976993</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8037038315631198</v>
+        <v>0.7561847197769109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.795512997548935</v>
+        <v>0.7541119588190393</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7955599858843205</v>
+        <v>0.7517457605014135</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7945794639877561</v>
+        <v>0.7208955209567975</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7928826097129684</v>
+        <v>0.7084829288500708</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7915439216272924</v>
+        <v>0.6871161820155502</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7914969332919068</v>
+        <v>0.6870222053447793</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7985370325619575</v>
+        <v>0.6844680536856116</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7975095223300077</v>
+        <v>0.6866170508202821</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7975095223300077</v>
+        <v>0.6866170508202821</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7976034990007786</v>
+        <v>0.6944497186453551</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8253640157573945</v>
+        <v>0.6721379309022144</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.826655715507685</v>
+        <v>0.6768410796960527</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8274952723980928</v>
+        <v>0.6757665811287173</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8421978266456466</v>
+        <v>0.6781035316049298</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8421978266456466</v>
+        <v>0.6952840013348524</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8361090014307468</v>
+        <v>0.6969338672742547</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8442820949509595</v>
+        <v>0.7017957215682213</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.844904450658412</v>
+        <v>0.6828901086677177</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8385859579674956</v>
+        <v>0.6828901086677177</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8434415791149315</v>
+        <v>0.6757152775380414</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8416977365047583</v>
+        <v>0.64850711345861</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.827565275428361</v>
+        <v>0.6547838920150516</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8185171440297964</v>
+        <v>0.6564630057958674</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8153291293157348</v>
+        <v>0.6552475422223756</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7977842602501697</v>
+        <v>0.6641662159622252</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7930048752795327</v>
+        <v>0.6949675492802154</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7865703501685827</v>
+        <v>0.6852563069853435</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7721027375979563</v>
+        <v>0.6812757237162594</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7721027375979563</v>
+        <v>0.6789095253986337</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7513290986294749</v>
+        <v>0.6850568462963602</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7341423957530216</v>
+        <v>0.6843405139181367</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7252707103485576</v>
+        <v>0.6848396451134049</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7430965504808154</v>
+        <v>0.6656698426945604</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7430965504808154</v>
+        <v>0.6483901220929564</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7510534017636927</v>
+        <v>0.6580073877170574</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7501491160439273</v>
+        <v>0.6597449971806999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7526562793677096</v>
+        <v>0.6659277990663706</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7574356643383466</v>
+        <v>0.6659277990663706</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7490036555007038</v>
+        <v>0.6406389646455929</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7490036555007038</v>
+        <v>0.6421656060728108</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7433199848103014</v>
+        <v>0.6460584458176546</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7101630015765066</v>
+        <v>0.6525169445691074</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7265561769523174</v>
+        <v>0.6003843454045408</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7273664860013118</v>
+        <v>0.6013639083554849</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6087362822829043</v>
+        <v>0.6442772043282969</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.606229118959122</v>
+        <v>0.6442772043282969</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6069454513373456</v>
+        <v>0.6515814931166883</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.577857753842495</v>
+        <v>0.6475591957131295</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5800067509771656</v>
+        <v>0.6374835540826151</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5863127773750206</v>
+        <v>0.6374835540826151</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5863127773750206</v>
+        <v>0.6214893000847708</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5829660571608305</v>
+        <v>0.6130165360582732</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5854732204846127</v>
+        <v>0.6130165360582732</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5854732204846127</v>
+        <v>0.5821495149653053</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5769242202813163</v>
+        <v>0.5809340513918136</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5840405557281657</v>
+        <v>0.5809340513918136</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5900938999551213</v>
+        <v>0.5805758852027019</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5932526668277696</v>
+        <v>0.5435907910534209</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5763133719213052</v>
+        <v>0.5173036942421069</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5770297042995286</v>
+        <v>0.5225644699140402</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5726554738533888</v>
+        <v>0.5232808022922636</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5676703950472376</v>
+        <v>0.5232808022922636</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5832125061851993</v>
+        <v>0.5104807961550116</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.586248048545663</v>
+        <v>0.5079266444958439</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5828658473435289</v>
+        <v>0.5086429768740675</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5953724161210266</v>
+        <v>0.505730659025788</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5993122442012558</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5861833197163056</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5951374744440993</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6200388948343518</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5962829349873228</v>
+        <v>0.5025071633237822</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6015906989946413</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5806008177888249</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5985561155797977</v>
+        <v>0.5068051575931232</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5993194362934067</v>
+        <v>0.5068051575931232</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5805298558129366</v>
+        <v>0.5096704871060171</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.579813523434713</v>
+        <v>0.5096704871060171</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6473137056343808</v>
+        <v>0.5079736328312294</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6476718718234926</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.6023338818502281</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6007310042462112</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5984117942639708</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5902271933963168</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5186577254577047</v>
+        <v>0.5039398280802292</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5211284488479228</v>
+        <v>0.504297994269341</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5188509530001573</v>
+        <v>0.5032704840373912</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5448959160423931</v>
+        <v>0.5032704840373912</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.537808828436957</v>
+        <v>0.4990194781034357</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5330054698258171</v>
+        <v>0.4996888221462737</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5333636360149289</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5309734640568002</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5315780792702808</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5074826526737322</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5074826526737322</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4954867224389439</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4958041334392009</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5381837761744207</v>
+        <v>0.5003581661891118</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5149029738821571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5146857726992018</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5130181662658274</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4998077314031676</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
